--- a/lab6/A5_1.xlsx
+++ b/lab6/A5_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merda\OneDrive\Рабочий стол\крипта 4 семак\lab6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hudaynazar\Desktop\крипта 4 семак\cryptografy\lab6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67843297-6B2D-4D18-AA4B-F65351E3C1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D54BEE9-11AB-4CA7-AA8E-96889DDAED75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="А5_1" sheetId="1" r:id="rId1"/>
@@ -543,15 +543,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1"/>
   <dimension ref="A1:EP319"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="11" customWidth="1"/>
-    <col min="2" max="81" width="2.77734375" customWidth="1"/>
-    <col min="82" max="82" width="2.44140625" customWidth="1"/>
-    <col min="83" max="146" width="6.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.85546875" style="11" customWidth="1"/>
+    <col min="2" max="81" width="2.7109375" customWidth="1"/>
+    <col min="82" max="82" width="2.42578125" customWidth="1"/>
+    <col min="83" max="146" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:146" s="7" customFormat="1" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:146" s="7" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
@@ -760,7 +760,7 @@
       <c r="BX1" s="6"/>
       <c r="BZ1" s="6"/>
     </row>
-    <row r="2" spans="1:146" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:146" ht="18.75" x14ac:dyDescent="0.3">
       <c r="CA2" s="4"/>
       <c r="CB2" s="9" t="s">
         <v>11</v>
@@ -836,7 +836,7 @@
       <c r="EO2" s="7"/>
       <c r="EP2" s="7"/>
     </row>
-    <row r="3" spans="1:146" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:146" ht="21" x14ac:dyDescent="0.35">
       <c r="AH3" s="5" t="s">
         <v>7</v>
       </c>
@@ -850,7 +850,7 @@
       <c r="CF3" s="4"/>
       <c r="CG3" s="4"/>
     </row>
-    <row r="4" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:146" x14ac:dyDescent="0.25">
       <c r="CA4" s="4"/>
       <c r="CB4" s="4"/>
       <c r="CC4" s="4"/>
@@ -861,7 +861,7 @@
       <c r="CF4" s="4"/>
       <c r="CG4" s="4"/>
     </row>
-    <row r="5" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:146" x14ac:dyDescent="0.25">
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
       <c r="AX5" s="4"/>
@@ -876,7 +876,7 @@
       <c r="CF5" s="4"/>
       <c r="CG5" s="4"/>
     </row>
-    <row r="6" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:146" x14ac:dyDescent="0.25">
       <c r="J6" t="s">
         <v>0</v>
       </c>
@@ -900,7 +900,7 @@
       <c r="CF6" s="4"/>
       <c r="CG6" s="4"/>
     </row>
-    <row r="7" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:146" x14ac:dyDescent="0.25">
       <c r="V7" s="4"/>
       <c r="W7" s="4" t="s">
         <v>12</v>
@@ -921,7 +921,7 @@
       <c r="CF7" s="4"/>
       <c r="CG7" s="4"/>
     </row>
-    <row r="8" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A8"/>
       <c r="B8">
         <v>0</v>
@@ -1127,7 +1127,7 @@
       <c r="CF8" s="4"/>
       <c r="CG8" s="4"/>
     </row>
-    <row r="9" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>0</v>
       </c>
@@ -1409,7 +1409,7 @@
       <c r="CF9" s="4"/>
       <c r="CG9" s="4"/>
     </row>
-    <row r="10" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>1</v>
       </c>
@@ -1691,7 +1691,7 @@
       <c r="CF10" s="4"/>
       <c r="CG10" s="4"/>
     </row>
-    <row r="11" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>2</v>
       </c>
@@ -1973,7 +1973,7 @@
       <c r="CF11" s="4"/>
       <c r="CG11" s="4"/>
     </row>
-    <row r="12" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>3</v>
       </c>
@@ -2255,7 +2255,7 @@
       <c r="CF12" s="4"/>
       <c r="CG12" s="4"/>
     </row>
-    <row r="13" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>4</v>
       </c>
@@ -2537,7 +2537,7 @@
       <c r="CF13" s="4"/>
       <c r="CG13" s="4"/>
     </row>
-    <row r="14" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>5</v>
       </c>
@@ -2821,7 +2821,7 @@
       <c r="CF14" s="4"/>
       <c r="CG14" s="4"/>
     </row>
-    <row r="15" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>6</v>
       </c>
@@ -3103,7 +3103,7 @@
       <c r="CF15" s="4"/>
       <c r="CG15" s="4"/>
     </row>
-    <row r="16" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:146" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>7</v>
       </c>
@@ -3385,7 +3385,7 @@
       <c r="CF16" s="4"/>
       <c r="CG16" s="4"/>
     </row>
-    <row r="17" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>8</v>
       </c>
@@ -3667,7 +3667,7 @@
       <c r="CF17" s="4"/>
       <c r="CG17" s="4"/>
     </row>
-    <row r="18" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>9</v>
       </c>
@@ -3949,7 +3949,7 @@
       <c r="CF18" s="4"/>
       <c r="CG18" s="4"/>
     </row>
-    <row r="19" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>10</v>
       </c>
@@ -4231,7 +4231,7 @@
       <c r="CF19" s="4"/>
       <c r="CG19" s="4"/>
     </row>
-    <row r="20" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>11</v>
       </c>
@@ -4515,7 +4515,7 @@
       <c r="CF20" s="4"/>
       <c r="CG20" s="4"/>
     </row>
-    <row r="21" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>12</v>
       </c>
@@ -4797,7 +4797,7 @@
       <c r="CF21" s="4"/>
       <c r="CG21" s="4"/>
     </row>
-    <row r="22" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>13</v>
       </c>
@@ -5079,7 +5079,7 @@
       <c r="CF22" s="4"/>
       <c r="CG22" s="4"/>
     </row>
-    <row r="23" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>14</v>
       </c>
@@ -5361,7 +5361,7 @@
       <c r="CF23" s="4"/>
       <c r="CG23" s="4"/>
     </row>
-    <row r="24" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>15</v>
       </c>
@@ -5643,7 +5643,7 @@
       <c r="CF24" s="4"/>
       <c r="CG24" s="4"/>
     </row>
-    <row r="25" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>16</v>
       </c>
@@ -5925,7 +5925,7 @@
       <c r="CF25" s="4"/>
       <c r="CG25" s="4"/>
     </row>
-    <row r="26" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>17</v>
       </c>
@@ -6209,7 +6209,7 @@
       <c r="CF26" s="4"/>
       <c r="CG26" s="4"/>
     </row>
-    <row r="27" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>18</v>
       </c>
@@ -6491,7 +6491,7 @@
       <c r="CF27" s="4"/>
       <c r="CG27" s="4"/>
     </row>
-    <row r="28" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>19</v>
       </c>
@@ -6773,7 +6773,7 @@
       <c r="CF28" s="4"/>
       <c r="CG28" s="4"/>
     </row>
-    <row r="29" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>20</v>
       </c>
@@ -7055,7 +7055,7 @@
       <c r="CF29" s="4"/>
       <c r="CG29" s="4"/>
     </row>
-    <row r="30" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>21</v>
       </c>
@@ -7337,7 +7337,7 @@
       <c r="CF30" s="4"/>
       <c r="CG30" s="4"/>
     </row>
-    <row r="31" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>22</v>
       </c>
@@ -7619,7 +7619,7 @@
       <c r="CF31" s="4"/>
       <c r="CG31" s="4"/>
     </row>
-    <row r="32" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>23</v>
       </c>
@@ -7903,7 +7903,7 @@
       <c r="CF32" s="4"/>
       <c r="CG32" s="4"/>
     </row>
-    <row r="33" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>24</v>
       </c>
@@ -8185,7 +8185,7 @@
       <c r="CF33" s="4"/>
       <c r="CG33" s="4"/>
     </row>
-    <row r="34" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>25</v>
       </c>
@@ -8467,7 +8467,7 @@
       <c r="CF34" s="4"/>
       <c r="CG34" s="4"/>
     </row>
-    <row r="35" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>26</v>
       </c>
@@ -8749,7 +8749,7 @@
       <c r="CF35" s="4"/>
       <c r="CG35" s="4"/>
     </row>
-    <row r="36" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>27</v>
       </c>
@@ -9031,7 +9031,7 @@
       <c r="CF36" s="4"/>
       <c r="CG36" s="4"/>
     </row>
-    <row r="37" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>28</v>
       </c>
@@ -9313,7 +9313,7 @@
       <c r="CF37" s="4"/>
       <c r="CG37" s="4"/>
     </row>
-    <row r="38" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>29</v>
       </c>
@@ -9597,7 +9597,7 @@
       <c r="CF38" s="4"/>
       <c r="CG38" s="4"/>
     </row>
-    <row r="39" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>30</v>
       </c>
@@ -9879,7 +9879,7 @@
       <c r="CF39" s="4"/>
       <c r="CG39" s="4"/>
     </row>
-    <row r="40" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>31</v>
       </c>
@@ -10161,7 +10161,7 @@
       <c r="CF40" s="4"/>
       <c r="CG40" s="4"/>
     </row>
-    <row r="41" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>32</v>
       </c>
@@ -10443,7 +10443,7 @@
       <c r="CF41" s="4"/>
       <c r="CG41" s="4"/>
     </row>
-    <row r="42" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>33</v>
       </c>
@@ -10725,7 +10725,7 @@
       <c r="CF42" s="4"/>
       <c r="CG42" s="4"/>
     </row>
-    <row r="43" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <v>34</v>
       </c>
@@ -11007,7 +11007,7 @@
       <c r="CF43" s="4"/>
       <c r="CG43" s="4"/>
     </row>
-    <row r="44" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
         <v>35</v>
       </c>
@@ -11291,7 +11291,7 @@
       <c r="CF44" s="4"/>
       <c r="CG44" s="4"/>
     </row>
-    <row r="45" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
         <v>36</v>
       </c>
@@ -11573,7 +11573,7 @@
       <c r="CF45" s="4"/>
       <c r="CG45" s="4"/>
     </row>
-    <row r="46" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
         <v>37</v>
       </c>
@@ -11855,7 +11855,7 @@
       <c r="CF46" s="4"/>
       <c r="CG46" s="4"/>
     </row>
-    <row r="47" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <v>38</v>
       </c>
@@ -12137,7 +12137,7 @@
       <c r="CF47" s="4"/>
       <c r="CG47" s="4"/>
     </row>
-    <row r="48" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>39</v>
       </c>
@@ -12419,7 +12419,7 @@
       <c r="CF48" s="4"/>
       <c r="CG48" s="4"/>
     </row>
-    <row r="49" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
         <v>40</v>
       </c>
@@ -12701,7 +12701,7 @@
       <c r="CF49" s="4"/>
       <c r="CG49" s="4"/>
     </row>
-    <row r="50" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
         <v>41</v>
       </c>
@@ -12985,7 +12985,7 @@
       <c r="CF50" s="4"/>
       <c r="CG50" s="4"/>
     </row>
-    <row r="51" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>42</v>
       </c>
@@ -13267,7 +13267,7 @@
       <c r="CF51" s="4"/>
       <c r="CG51" s="4"/>
     </row>
-    <row r="52" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>43</v>
       </c>
@@ -13549,7 +13549,7 @@
       <c r="CF52" s="4"/>
       <c r="CG52" s="4"/>
     </row>
-    <row r="53" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
         <v>44</v>
       </c>
@@ -13831,7 +13831,7 @@
       <c r="CF53" s="4"/>
       <c r="CG53" s="4"/>
     </row>
-    <row r="54" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
         <v>45</v>
       </c>
@@ -14113,7 +14113,7 @@
       <c r="CF54" s="4"/>
       <c r="CG54" s="4"/>
     </row>
-    <row r="55" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
         <v>46</v>
       </c>
@@ -14395,7 +14395,7 @@
       <c r="CF55" s="4"/>
       <c r="CG55" s="4"/>
     </row>
-    <row r="56" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
         <v>47</v>
       </c>
@@ -14679,7 +14679,7 @@
       <c r="CF56" s="4"/>
       <c r="CG56" s="4"/>
     </row>
-    <row r="57" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
         <v>48</v>
       </c>
@@ -14961,7 +14961,7 @@
       <c r="CF57" s="4"/>
       <c r="CG57" s="4"/>
     </row>
-    <row r="58" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>49</v>
       </c>
@@ -15243,7 +15243,7 @@
       <c r="CF58" s="4"/>
       <c r="CG58" s="4"/>
     </row>
-    <row r="59" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
         <v>50</v>
       </c>
@@ -15525,7 +15525,7 @@
       <c r="CF59" s="4"/>
       <c r="CG59" s="4"/>
     </row>
-    <row r="60" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
         <v>51</v>
       </c>
@@ -15807,7 +15807,7 @@
       <c r="CF60" s="4"/>
       <c r="CG60" s="4"/>
     </row>
-    <row r="61" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
         <v>52</v>
       </c>
@@ -16089,7 +16089,7 @@
       <c r="CF61" s="4"/>
       <c r="CG61" s="4"/>
     </row>
-    <row r="62" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
         <v>53</v>
       </c>
@@ -16371,7 +16371,7 @@
       <c r="CF62" s="4"/>
       <c r="CG62" s="4"/>
     </row>
-    <row r="63" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
         <v>54</v>
       </c>
@@ -16653,7 +16653,7 @@
       <c r="CF63" s="4"/>
       <c r="CG63" s="4"/>
     </row>
-    <row r="64" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
         <v>55</v>
       </c>
@@ -16935,7 +16935,7 @@
       <c r="CF64" s="4"/>
       <c r="CG64" s="4"/>
     </row>
-    <row r="65" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
         <v>56</v>
       </c>
@@ -17217,7 +17217,7 @@
       <c r="CF65" s="4"/>
       <c r="CG65" s="4"/>
     </row>
-    <row r="66" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
         <v>57</v>
       </c>
@@ -17497,7 +17497,7 @@
       <c r="CF66" s="4"/>
       <c r="CG66" s="4"/>
     </row>
-    <row r="67" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
         <v>58</v>
       </c>
@@ -17777,7 +17777,7 @@
       <c r="CF67" s="4"/>
       <c r="CG67" s="4"/>
     </row>
-    <row r="68" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A68" s="11">
         <v>59</v>
       </c>
@@ -18057,7 +18057,7 @@
       <c r="CF68" s="4"/>
       <c r="CG68" s="4"/>
     </row>
-    <row r="69" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A69" s="11">
         <v>60</v>
       </c>
@@ -18337,7 +18337,7 @@
       <c r="CF69" s="4"/>
       <c r="CG69" s="4"/>
     </row>
-    <row r="70" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A70" s="11">
         <v>61</v>
       </c>
@@ -18617,7 +18617,7 @@
       <c r="CF70" s="4"/>
       <c r="CG70" s="4"/>
     </row>
-    <row r="71" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
         <v>62</v>
       </c>
@@ -18897,7 +18897,7 @@
       <c r="CF71" s="4"/>
       <c r="CG71" s="4"/>
     </row>
-    <row r="72" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A72" s="11">
         <v>63</v>
       </c>
@@ -19177,7 +19177,7 @@
       <c r="CF72" s="4"/>
       <c r="CG72" s="4"/>
     </row>
-    <row r="73" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
         <v>64</v>
       </c>
@@ -19457,7 +19457,7 @@
       <c r="CF73" s="4"/>
       <c r="CG73" s="4"/>
     </row>
-    <row r="74" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
         <v>65</v>
       </c>
@@ -19737,7 +19737,7 @@
       <c r="CF74" s="4"/>
       <c r="CG74" s="4"/>
     </row>
-    <row r="75" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A75" s="11">
         <v>66</v>
       </c>
@@ -20017,7 +20017,7 @@
       <c r="CF75" s="4"/>
       <c r="CG75" s="4"/>
     </row>
-    <row r="76" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A76" s="11">
         <v>67</v>
       </c>
@@ -20297,7 +20297,7 @@
       <c r="CF76" s="4"/>
       <c r="CG76" s="4"/>
     </row>
-    <row r="77" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A77" s="11">
         <v>68</v>
       </c>
@@ -20577,7 +20577,7 @@
       <c r="CF77" s="4"/>
       <c r="CG77" s="4"/>
     </row>
-    <row r="78" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A78" s="11">
         <v>69</v>
       </c>
@@ -20857,7 +20857,7 @@
       <c r="CF78" s="4"/>
       <c r="CG78" s="4"/>
     </row>
-    <row r="79" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A79" s="11">
         <v>70</v>
       </c>
@@ -21137,7 +21137,7 @@
       <c r="CF79" s="4"/>
       <c r="CG79" s="4"/>
     </row>
-    <row r="80" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A80" s="11">
         <v>71</v>
       </c>
@@ -21417,7 +21417,7 @@
       <c r="CF80" s="4"/>
       <c r="CG80" s="4"/>
     </row>
-    <row r="81" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A81" s="11">
         <v>72</v>
       </c>
@@ -21697,7 +21697,7 @@
       <c r="CF81" s="4"/>
       <c r="CG81" s="4"/>
     </row>
-    <row r="82" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A82" s="11">
         <v>73</v>
       </c>
@@ -21977,7 +21977,7 @@
       <c r="CF82" s="4"/>
       <c r="CG82" s="4"/>
     </row>
-    <row r="83" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A83" s="11">
         <v>74</v>
       </c>
@@ -22257,7 +22257,7 @@
       <c r="CF83" s="4"/>
       <c r="CG83" s="4"/>
     </row>
-    <row r="84" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A84" s="11">
         <v>75</v>
       </c>
@@ -22537,7 +22537,7 @@
       <c r="CF84" s="4"/>
       <c r="CG84" s="4"/>
     </row>
-    <row r="85" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A85" s="11">
         <v>76</v>
       </c>
@@ -22817,7 +22817,7 @@
       <c r="CF85" s="4"/>
       <c r="CG85" s="4"/>
     </row>
-    <row r="86" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A86" s="11">
         <v>77</v>
       </c>
@@ -23097,7 +23097,7 @@
       <c r="CF86" s="4"/>
       <c r="CG86" s="4"/>
     </row>
-    <row r="87" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A87" s="11">
         <v>78</v>
       </c>
@@ -23377,7 +23377,7 @@
       <c r="CF87" s="4"/>
       <c r="CG87" s="4"/>
     </row>
-    <row r="88" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A88" s="11">
         <v>79</v>
       </c>
@@ -23657,7 +23657,7 @@
       <c r="CF88" s="4"/>
       <c r="CG88" s="4"/>
     </row>
-    <row r="89" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A89" s="11">
         <v>80</v>
       </c>
@@ -23937,7 +23937,7 @@
       <c r="CF89" s="4"/>
       <c r="CG89" s="4"/>
     </row>
-    <row r="90" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A90" s="11">
         <v>81</v>
       </c>
@@ -24217,7 +24217,7 @@
       <c r="CF90" s="4"/>
       <c r="CG90" s="4"/>
     </row>
-    <row r="91" spans="1:98" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:98" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="11">
         <v>82</v>
       </c>
@@ -24520,7 +24520,7 @@
       <c r="CS91"/>
       <c r="CT91"/>
     </row>
-    <row r="92" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A92" s="11">
         <v>83</v>
       </c>
@@ -24800,7 +24800,7 @@
       <c r="CF92" s="4"/>
       <c r="CG92" s="4"/>
     </row>
-    <row r="93" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A93" s="11">
         <v>84</v>
       </c>
@@ -25080,7 +25080,7 @@
       <c r="CF93" s="4"/>
       <c r="CG93" s="4"/>
     </row>
-    <row r="94" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A94" s="11">
         <v>85</v>
       </c>
@@ -25357,7 +25357,7 @@
       <c r="CF94" s="4"/>
       <c r="CG94" s="4"/>
     </row>
-    <row r="95" spans="1:98" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:98" x14ac:dyDescent="0.25">
       <c r="CA95" s="4"/>
       <c r="CB95" s="4"/>
       <c r="CC95" s="4"/>
@@ -25366,7 +25366,7 @@
       <c r="CF95" s="4"/>
       <c r="CG95" s="4"/>
     </row>
-    <row r="96" spans="1:98" ht="21" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:98" ht="21" x14ac:dyDescent="0.35">
       <c r="AG96" s="5" t="s">
         <v>4</v>
       </c>
@@ -25378,7 +25378,7 @@
       <c r="CF96" s="4"/>
       <c r="CG96" s="4"/>
     </row>
-    <row r="97" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:85" x14ac:dyDescent="0.25">
       <c r="CA97" s="4"/>
       <c r="CB97" s="4"/>
       <c r="CC97" s="4"/>
@@ -25387,7 +25387,7 @@
       <c r="CF97" s="4"/>
       <c r="CG97" s="4"/>
     </row>
-    <row r="98" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:85" x14ac:dyDescent="0.25">
       <c r="W98" s="4" t="s">
         <v>5</v>
       </c>
@@ -25400,7 +25400,7 @@
       <c r="CF98" s="4"/>
       <c r="CG98" s="4"/>
     </row>
-    <row r="99" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="B99">
         <f t="shared" ref="B99:S99" si="101">B94</f>
@@ -25663,7 +25663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A100" s="11">
         <v>0</v>
       </c>
@@ -25935,7 +25935,7 @@
       <c r="CF100" s="4"/>
       <c r="CG100" s="4"/>
     </row>
-    <row r="101" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A101" s="11">
         <v>1</v>
       </c>
@@ -26207,7 +26207,7 @@
       <c r="CF101" s="4"/>
       <c r="CG101" s="4"/>
     </row>
-    <row r="102" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A102" s="11">
         <v>2</v>
       </c>
@@ -26479,7 +26479,7 @@
       <c r="CF102" s="4"/>
       <c r="CG102" s="4"/>
     </row>
-    <row r="103" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A103" s="11">
         <v>3</v>
       </c>
@@ -26754,7 +26754,7 @@
       <c r="CF103" s="4"/>
       <c r="CG103" s="4"/>
     </row>
-    <row r="104" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A104" s="11">
         <v>4</v>
       </c>
@@ -27026,7 +27026,7 @@
       <c r="CF104" s="4"/>
       <c r="CG104" s="4"/>
     </row>
-    <row r="105" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A105" s="11">
         <v>5</v>
       </c>
@@ -27298,7 +27298,7 @@
       <c r="CF105" s="4"/>
       <c r="CG105" s="4"/>
     </row>
-    <row r="106" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A106" s="11">
         <v>6</v>
       </c>
@@ -27570,7 +27570,7 @@
       <c r="CF106" s="4"/>
       <c r="CG106" s="4"/>
     </row>
-    <row r="107" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A107" s="11">
         <v>7</v>
       </c>
@@ -27842,7 +27842,7 @@
       <c r="CF107" s="4"/>
       <c r="CG107" s="4"/>
     </row>
-    <row r="108" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A108" s="11">
         <v>8</v>
       </c>
@@ -28114,7 +28114,7 @@
       <c r="CF108" s="4"/>
       <c r="CG108" s="4"/>
     </row>
-    <row r="109" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A109" s="11">
         <v>9</v>
       </c>
@@ -28386,7 +28386,7 @@
       <c r="CF109" s="4"/>
       <c r="CG109" s="4"/>
     </row>
-    <row r="110" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A110" s="11">
         <v>10</v>
       </c>
@@ -28658,7 +28658,7 @@
       <c r="CF110" s="4"/>
       <c r="CG110" s="4"/>
     </row>
-    <row r="111" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A111" s="11">
         <v>11</v>
       </c>
@@ -28930,7 +28930,7 @@
       <c r="CF111" s="4"/>
       <c r="CG111" s="4"/>
     </row>
-    <row r="112" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A112" s="11">
         <v>12</v>
       </c>
@@ -29202,7 +29202,7 @@
       <c r="CF112" s="4"/>
       <c r="CG112" s="4"/>
     </row>
-    <row r="113" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A113" s="11">
         <v>13</v>
       </c>
@@ -29474,7 +29474,7 @@
       <c r="CF113" s="4"/>
       <c r="CG113" s="4"/>
     </row>
-    <row r="114" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A114" s="11">
         <v>14</v>
       </c>
@@ -29746,7 +29746,7 @@
       <c r="CF114" s="4"/>
       <c r="CG114" s="4"/>
     </row>
-    <row r="115" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A115" s="11">
         <v>15</v>
       </c>
@@ -30018,7 +30018,7 @@
       <c r="CF115" s="4"/>
       <c r="CG115" s="4"/>
     </row>
-    <row r="116" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A116" s="11">
         <v>16</v>
       </c>
@@ -30290,7 +30290,7 @@
       <c r="CF116" s="4"/>
       <c r="CG116" s="4"/>
     </row>
-    <row r="117" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A117" s="11">
         <v>17</v>
       </c>
@@ -30562,7 +30562,7 @@
       <c r="CF117" s="4"/>
       <c r="CG117" s="4"/>
     </row>
-    <row r="118" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A118" s="11">
         <v>18</v>
       </c>
@@ -30834,7 +30834,7 @@
       <c r="CF118" s="4"/>
       <c r="CG118" s="4"/>
     </row>
-    <row r="119" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A119" s="11">
         <v>19</v>
       </c>
@@ -31106,7 +31106,7 @@
       <c r="CF119" s="4"/>
       <c r="CG119" s="4"/>
     </row>
-    <row r="120" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A120" s="11">
         <v>20</v>
       </c>
@@ -31378,7 +31378,7 @@
       <c r="CF120" s="4"/>
       <c r="CG120" s="4"/>
     </row>
-    <row r="121" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A121" s="11">
         <v>21</v>
       </c>
@@ -31650,7 +31650,7 @@
       <c r="CF121" s="4"/>
       <c r="CG121" s="4"/>
     </row>
-    <row r="122" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A122" s="11">
         <v>22</v>
       </c>
@@ -31922,7 +31922,7 @@
       <c r="CF122" s="4"/>
       <c r="CG122" s="4"/>
     </row>
-    <row r="123" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A123" s="11">
         <v>23</v>
       </c>
@@ -32194,7 +32194,7 @@
       <c r="CF123" s="4"/>
       <c r="CG123" s="4"/>
     </row>
-    <row r="124" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A124" s="11">
         <v>24</v>
       </c>
@@ -32466,7 +32466,7 @@
       <c r="CF124" s="4"/>
       <c r="CG124" s="4"/>
     </row>
-    <row r="125" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A125" s="11">
         <v>25</v>
       </c>
@@ -32738,7 +32738,7 @@
       <c r="CF125" s="4"/>
       <c r="CG125" s="4"/>
     </row>
-    <row r="126" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A126" s="11">
         <v>26</v>
       </c>
@@ -33010,7 +33010,7 @@
       <c r="CF126" s="4"/>
       <c r="CG126" s="4"/>
     </row>
-    <row r="127" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A127" s="11">
         <v>27</v>
       </c>
@@ -33282,7 +33282,7 @@
       <c r="CF127" s="4"/>
       <c r="CG127" s="4"/>
     </row>
-    <row r="128" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A128" s="11">
         <v>28</v>
       </c>
@@ -33554,7 +33554,7 @@
       <c r="CF128" s="4"/>
       <c r="CG128" s="4"/>
     </row>
-    <row r="129" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A129" s="11">
         <v>29</v>
       </c>
@@ -33826,7 +33826,7 @@
       <c r="CF129" s="4"/>
       <c r="CG129" s="4"/>
     </row>
-    <row r="130" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A130" s="11">
         <v>30</v>
       </c>
@@ -34098,7 +34098,7 @@
       <c r="CF130" s="4"/>
       <c r="CG130" s="4"/>
     </row>
-    <row r="131" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A131" s="11">
         <v>31</v>
       </c>
@@ -34370,7 +34370,7 @@
       <c r="CF131" s="4"/>
       <c r="CG131" s="4"/>
     </row>
-    <row r="132" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A132" s="11">
         <v>32</v>
       </c>
@@ -34642,7 +34642,7 @@
       <c r="CF132" s="4"/>
       <c r="CG132" s="4"/>
     </row>
-    <row r="133" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A133" s="11">
         <v>33</v>
       </c>
@@ -34914,7 +34914,7 @@
       <c r="CF133" s="4"/>
       <c r="CG133" s="4"/>
     </row>
-    <row r="134" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A134" s="11">
         <v>34</v>
       </c>
@@ -35186,7 +35186,7 @@
       <c r="CF134" s="4"/>
       <c r="CG134" s="4"/>
     </row>
-    <row r="135" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A135" s="11">
         <v>35</v>
       </c>
@@ -35458,7 +35458,7 @@
       <c r="CF135" s="4"/>
       <c r="CG135" s="4"/>
     </row>
-    <row r="136" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A136" s="11">
         <v>36</v>
       </c>
@@ -35730,7 +35730,7 @@
       <c r="CF136" s="4"/>
       <c r="CG136" s="4"/>
     </row>
-    <row r="137" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A137" s="11">
         <v>37</v>
       </c>
@@ -36002,7 +36002,7 @@
       <c r="CF137" s="4"/>
       <c r="CG137" s="4"/>
     </row>
-    <row r="138" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A138" s="11">
         <v>38</v>
       </c>
@@ -36274,7 +36274,7 @@
       <c r="CF138" s="4"/>
       <c r="CG138" s="4"/>
     </row>
-    <row r="139" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A139" s="11">
         <v>39</v>
       </c>
@@ -36546,7 +36546,7 @@
       <c r="CF139" s="4"/>
       <c r="CG139" s="4"/>
     </row>
-    <row r="140" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A140" s="11">
         <v>40</v>
       </c>
@@ -36818,7 +36818,7 @@
       <c r="CF140" s="4"/>
       <c r="CG140" s="4"/>
     </row>
-    <row r="141" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A141" s="11">
         <v>41</v>
       </c>
@@ -37090,7 +37090,7 @@
       <c r="CF141" s="4"/>
       <c r="CG141" s="4"/>
     </row>
-    <row r="142" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A142" s="11">
         <v>42</v>
       </c>
@@ -37362,7 +37362,7 @@
       <c r="CF142" s="4"/>
       <c r="CG142" s="4"/>
     </row>
-    <row r="143" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A143" s="11">
         <v>43</v>
       </c>
@@ -37634,7 +37634,7 @@
       <c r="CF143" s="4"/>
       <c r="CG143" s="4"/>
     </row>
-    <row r="144" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A144" s="11">
         <v>44</v>
       </c>
@@ -37906,7 +37906,7 @@
       <c r="CF144" s="4"/>
       <c r="CG144" s="4"/>
     </row>
-    <row r="145" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A145" s="11">
         <v>45</v>
       </c>
@@ -38178,7 +38178,7 @@
       <c r="CF145" s="4"/>
       <c r="CG145" s="4"/>
     </row>
-    <row r="146" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A146" s="11">
         <v>46</v>
       </c>
@@ -38450,7 +38450,7 @@
       <c r="CF146" s="4"/>
       <c r="CG146" s="4"/>
     </row>
-    <row r="147" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A147" s="11">
         <v>47</v>
       </c>
@@ -38722,7 +38722,7 @@
       <c r="CF147" s="4"/>
       <c r="CG147" s="4"/>
     </row>
-    <row r="148" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A148" s="11">
         <v>48</v>
       </c>
@@ -38994,7 +38994,7 @@
       <c r="CF148" s="4"/>
       <c r="CG148" s="4"/>
     </row>
-    <row r="149" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A149" s="11">
         <v>49</v>
       </c>
@@ -39266,7 +39266,7 @@
       <c r="CF149" s="4"/>
       <c r="CG149" s="4"/>
     </row>
-    <row r="150" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A150" s="11">
         <v>50</v>
       </c>
@@ -39538,7 +39538,7 @@
       <c r="CF150" s="4"/>
       <c r="CG150" s="4"/>
     </row>
-    <row r="151" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A151" s="11">
         <v>51</v>
       </c>
@@ -39810,7 +39810,7 @@
       <c r="CF151" s="4"/>
       <c r="CG151" s="4"/>
     </row>
-    <row r="152" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A152" s="11">
         <v>52</v>
       </c>
@@ -40082,7 +40082,7 @@
       <c r="CF152" s="4"/>
       <c r="CG152" s="4"/>
     </row>
-    <row r="153" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A153" s="11">
         <v>53</v>
       </c>
@@ -40354,7 +40354,7 @@
       <c r="CF153" s="4"/>
       <c r="CG153" s="4"/>
     </row>
-    <row r="154" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A154" s="11">
         <v>54</v>
       </c>
@@ -40626,7 +40626,7 @@
       <c r="CF154" s="4"/>
       <c r="CG154" s="4"/>
     </row>
-    <row r="155" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A155" s="11">
         <v>55</v>
       </c>
@@ -40898,7 +40898,7 @@
       <c r="CF155" s="4"/>
       <c r="CG155" s="4"/>
     </row>
-    <row r="156" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A156" s="11">
         <v>56</v>
       </c>
@@ -41170,7 +41170,7 @@
       <c r="CF156" s="4"/>
       <c r="CG156" s="4"/>
     </row>
-    <row r="157" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A157" s="11">
         <v>57</v>
       </c>
@@ -41442,7 +41442,7 @@
       <c r="CF157" s="4"/>
       <c r="CG157" s="4"/>
     </row>
-    <row r="158" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A158" s="11">
         <v>58</v>
       </c>
@@ -41714,7 +41714,7 @@
       <c r="CF158" s="4"/>
       <c r="CG158" s="4"/>
     </row>
-    <row r="159" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A159" s="11">
         <v>59</v>
       </c>
@@ -41986,7 +41986,7 @@
       <c r="CF159" s="4"/>
       <c r="CG159" s="4"/>
     </row>
-    <row r="160" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A160" s="11">
         <v>60</v>
       </c>
@@ -42258,7 +42258,7 @@
       <c r="CF160" s="4"/>
       <c r="CG160" s="4"/>
     </row>
-    <row r="161" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A161" s="11">
         <v>61</v>
       </c>
@@ -42530,7 +42530,7 @@
       <c r="CF161" s="4"/>
       <c r="CG161" s="4"/>
     </row>
-    <row r="162" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A162" s="11">
         <v>62</v>
       </c>
@@ -42802,7 +42802,7 @@
       <c r="CF162" s="4"/>
       <c r="CG162" s="4"/>
     </row>
-    <row r="163" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A163" s="11">
         <v>63</v>
       </c>
@@ -43074,7 +43074,7 @@
       <c r="CF163" s="4"/>
       <c r="CG163" s="4"/>
     </row>
-    <row r="164" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A164" s="11">
         <v>64</v>
       </c>
@@ -43346,7 +43346,7 @@
       <c r="CF164" s="4"/>
       <c r="CG164" s="4"/>
     </row>
-    <row r="165" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A165" s="11">
         <v>65</v>
       </c>
@@ -43618,7 +43618,7 @@
       <c r="CF165" s="4"/>
       <c r="CG165" s="4"/>
     </row>
-    <row r="166" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A166" s="11">
         <v>66</v>
       </c>
@@ -43890,7 +43890,7 @@
       <c r="CF166" s="4"/>
       <c r="CG166" s="4"/>
     </row>
-    <row r="167" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A167" s="11">
         <v>67</v>
       </c>
@@ -44162,7 +44162,7 @@
       <c r="CF167" s="4"/>
       <c r="CG167" s="4"/>
     </row>
-    <row r="168" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A168" s="11">
         <v>68</v>
       </c>
@@ -44434,7 +44434,7 @@
       <c r="CF168" s="4"/>
       <c r="CG168" s="4"/>
     </row>
-    <row r="169" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A169" s="11">
         <v>69</v>
       </c>
@@ -44706,7 +44706,7 @@
       <c r="CF169" s="4"/>
       <c r="CG169" s="4"/>
     </row>
-    <row r="170" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A170" s="11">
         <v>70</v>
       </c>
@@ -44978,7 +44978,7 @@
       <c r="CF170" s="4"/>
       <c r="CG170" s="4"/>
     </row>
-    <row r="171" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A171" s="11">
         <v>71</v>
       </c>
@@ -45250,7 +45250,7 @@
       <c r="CF171" s="4"/>
       <c r="CG171" s="4"/>
     </row>
-    <row r="172" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A172" s="11">
         <v>72</v>
       </c>
@@ -45522,7 +45522,7 @@
       <c r="CF172" s="4"/>
       <c r="CG172" s="4"/>
     </row>
-    <row r="173" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A173" s="11">
         <v>73</v>
       </c>
@@ -45794,7 +45794,7 @@
       <c r="CF173" s="4"/>
       <c r="CG173" s="4"/>
     </row>
-    <row r="174" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A174" s="11">
         <v>74</v>
       </c>
@@ -46066,7 +46066,7 @@
       <c r="CF174" s="4"/>
       <c r="CG174" s="4"/>
     </row>
-    <row r="175" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A175" s="11">
         <v>75</v>
       </c>
@@ -46338,7 +46338,7 @@
       <c r="CF175" s="4"/>
       <c r="CG175" s="4"/>
     </row>
-    <row r="176" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A176" s="11">
         <v>76</v>
       </c>
@@ -46610,7 +46610,7 @@
       <c r="CF176" s="4"/>
       <c r="CG176" s="4"/>
     </row>
-    <row r="177" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A177" s="11">
         <v>77</v>
       </c>
@@ -46882,7 +46882,7 @@
       <c r="CF177" s="4"/>
       <c r="CG177" s="4"/>
     </row>
-    <row r="178" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A178" s="11">
         <v>78</v>
       </c>
@@ -47154,7 +47154,7 @@
       <c r="CF178" s="4"/>
       <c r="CG178" s="4"/>
     </row>
-    <row r="179" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A179" s="11">
         <v>79</v>
       </c>
@@ -47426,7 +47426,7 @@
       <c r="CF179" s="4"/>
       <c r="CG179" s="4"/>
     </row>
-    <row r="180" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A180" s="11">
         <v>80</v>
       </c>
@@ -47698,7 +47698,7 @@
       <c r="CF180" s="4"/>
       <c r="CG180" s="4"/>
     </row>
-    <row r="181" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A181" s="11">
         <v>81</v>
       </c>
@@ -47970,7 +47970,7 @@
       <c r="CF181" s="4"/>
       <c r="CG181" s="4"/>
     </row>
-    <row r="182" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A182" s="11">
         <v>82</v>
       </c>
@@ -48242,7 +48242,7 @@
       <c r="CF182" s="4"/>
       <c r="CG182" s="4"/>
     </row>
-    <row r="183" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A183" s="11">
         <v>83</v>
       </c>
@@ -48514,7 +48514,7 @@
       <c r="CF183" s="4"/>
       <c r="CG183" s="4"/>
     </row>
-    <row r="184" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A184" s="11">
         <v>84</v>
       </c>
@@ -48786,7 +48786,7 @@
       <c r="CF184" s="4"/>
       <c r="CG184" s="4"/>
     </row>
-    <row r="185" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A185" s="11">
         <v>85</v>
       </c>
@@ -49058,7 +49058,7 @@
       <c r="CF185" s="4"/>
       <c r="CG185" s="4"/>
     </row>
-    <row r="186" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A186" s="11">
         <v>86</v>
       </c>
@@ -49330,7 +49330,7 @@
       <c r="CF186" s="4"/>
       <c r="CG186" s="4"/>
     </row>
-    <row r="187" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A187" s="11">
         <v>87</v>
       </c>
@@ -49602,7 +49602,7 @@
       <c r="CF187" s="4"/>
       <c r="CG187" s="4"/>
     </row>
-    <row r="188" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A188" s="11">
         <v>88</v>
       </c>
@@ -49874,7 +49874,7 @@
       <c r="CF188" s="4"/>
       <c r="CG188" s="4"/>
     </row>
-    <row r="189" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A189" s="11">
         <v>89</v>
       </c>
@@ -50146,7 +50146,7 @@
       <c r="CF189" s="4"/>
       <c r="CG189" s="4"/>
     </row>
-    <row r="190" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A190" s="11">
         <v>90</v>
       </c>
@@ -50418,7 +50418,7 @@
       <c r="CF190" s="4"/>
       <c r="CG190" s="4"/>
     </row>
-    <row r="191" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A191" s="11">
         <v>91</v>
       </c>
@@ -50690,7 +50690,7 @@
       <c r="CF191" s="4"/>
       <c r="CG191" s="4"/>
     </row>
-    <row r="192" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A192" s="11">
         <v>92</v>
       </c>
@@ -50962,7 +50962,7 @@
       <c r="CF192" s="4"/>
       <c r="CG192" s="4"/>
     </row>
-    <row r="193" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A193" s="11">
         <v>93</v>
       </c>
@@ -51234,7 +51234,7 @@
       <c r="CF193" s="4"/>
       <c r="CG193" s="4"/>
     </row>
-    <row r="194" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A194" s="11">
         <v>94</v>
       </c>
@@ -51506,7 +51506,7 @@
       <c r="CF194" s="4"/>
       <c r="CG194" s="4"/>
     </row>
-    <row r="195" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A195" s="11">
         <v>95</v>
       </c>
@@ -51778,7 +51778,7 @@
       <c r="CF195" s="4"/>
       <c r="CG195" s="4"/>
     </row>
-    <row r="196" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A196" s="11">
         <v>96</v>
       </c>
@@ -52050,7 +52050,7 @@
       <c r="CF196" s="4"/>
       <c r="CG196" s="4"/>
     </row>
-    <row r="197" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A197" s="11">
         <v>97</v>
       </c>
@@ -52322,7 +52322,7 @@
       <c r="CF197" s="4"/>
       <c r="CG197" s="4"/>
     </row>
-    <row r="198" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A198" s="11">
         <v>98</v>
       </c>
@@ -52594,7 +52594,7 @@
       <c r="CF198" s="4"/>
       <c r="CG198" s="4"/>
     </row>
-    <row r="199" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A199" s="11">
         <v>99</v>
       </c>
@@ -52866,7 +52866,7 @@
       <c r="CF199" s="4"/>
       <c r="CG199" s="4"/>
     </row>
-    <row r="200" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:86" x14ac:dyDescent="0.25">
       <c r="CA200" s="4"/>
       <c r="CB200" s="4"/>
       <c r="CC200" s="4"/>
@@ -52875,7 +52875,7 @@
       <c r="CF200" s="4"/>
       <c r="CG200" s="4"/>
     </row>
-    <row r="201" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:86" x14ac:dyDescent="0.25">
       <c r="CA201" s="4"/>
       <c r="CB201" s="4"/>
       <c r="CC201" s="4"/>
@@ -52884,7 +52884,7 @@
       <c r="CF201" s="4"/>
       <c r="CG201" s="4"/>
     </row>
-    <row r="202" spans="1:86" ht="21" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:86" ht="21" x14ac:dyDescent="0.35">
       <c r="AJ202" s="5" t="s">
         <v>6</v>
       </c>
@@ -52896,7 +52896,7 @@
       <c r="CF202" s="4"/>
       <c r="CG202" s="4"/>
     </row>
-    <row r="203" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:86" x14ac:dyDescent="0.25">
       <c r="CA203" s="4"/>
       <c r="CB203" s="4"/>
       <c r="CC203" s="4"/>
@@ -52905,7 +52905,7 @@
       <c r="CF203" s="4"/>
       <c r="CG203" s="4"/>
     </row>
-    <row r="204" spans="1:86" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:86" ht="15.75" x14ac:dyDescent="0.25">
       <c r="W204" s="4" t="s">
         <v>5</v>
       </c>
@@ -52923,7 +52923,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="205" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A205"/>
       <c r="B205">
         <f t="shared" ref="B205:T205" si="296">B199</f>
@@ -53216,7 +53216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A206" s="11">
         <v>0</v>
       </c>
@@ -53501,7 +53501,7 @@
         <v>0</v>
       </c>
       <c r="CF206" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG206" s="4">
         <v>1</v>
@@ -53510,7 +53510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A207" s="11">
         <v>1</v>
       </c>
@@ -53795,7 +53795,7 @@
         <v>0</v>
       </c>
       <c r="CF207" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG207" s="4">
         <v>1</v>
@@ -53804,7 +53804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A208" s="11">
         <v>2</v>
       </c>
@@ -54089,7 +54089,7 @@
         <v>1</v>
       </c>
       <c r="CF208" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG208" s="4">
         <v>0</v>
@@ -54098,7 +54098,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A209" s="11">
         <v>3</v>
       </c>
@@ -54383,7 +54383,7 @@
         <v>1</v>
       </c>
       <c r="CF209" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG209" s="4">
         <v>0</v>
@@ -54392,7 +54392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A210" s="11">
         <v>4</v>
       </c>
@@ -54686,7 +54686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A211" s="11">
         <v>5</v>
       </c>
@@ -54980,7 +54980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A212" s="11">
         <v>6</v>
       </c>
@@ -55265,17 +55265,16 @@
         <v>1</v>
       </c>
       <c r="CF212" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG212" s="4">
-        <f t="shared" ref="CG207:CG219" si="368">IF(_xlfn.XOR(CE212,CF212),1,0)</f>
         <v>1</v>
       </c>
       <c r="CH212">
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A213" s="11">
         <v>7</v>
       </c>
@@ -55560,7 +55559,7 @@
         <v>0</v>
       </c>
       <c r="CF213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG213" s="4">
         <v>1</v>
@@ -55569,7 +55568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A214" s="11">
         <v>8</v>
       </c>
@@ -55857,14 +55856,14 @@
         <v>0</v>
       </c>
       <c r="CG214" s="4">
-        <f t="shared" si="368"/>
+        <f t="shared" ref="CG212:CG219" si="368">IF(_xlfn.XOR(CE214,CF214),1,0)</f>
         <v>0</v>
       </c>
       <c r="CH214">
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A215" s="11">
         <v>9</v>
       </c>
@@ -56152,14 +56151,13 @@
         <v>1</v>
       </c>
       <c r="CG215" s="4">
-        <f t="shared" si="368"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH215">
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A216" s="11">
         <v>10</v>
       </c>
@@ -56453,7 +56451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A217" s="11">
         <v>11</v>
       </c>
@@ -56741,13 +56739,13 @@
         <v>1</v>
       </c>
       <c r="CG217" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH217">
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A218" s="11">
         <v>12</v>
       </c>
@@ -57032,17 +57030,16 @@
         <v>1</v>
       </c>
       <c r="CF218" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG218" s="4">
-        <f t="shared" si="368"/>
         <v>0</v>
       </c>
       <c r="CH218">
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A219" s="11">
         <v>13</v>
       </c>
@@ -57337,7 +57334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A220" s="11">
         <v>14</v>
       </c>
@@ -57624,7 +57621,7 @@
       <c r="CF220" s="4"/>
       <c r="CG220" s="4"/>
     </row>
-    <row r="221" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A221" s="11">
         <v>15</v>
       </c>
@@ -57911,7 +57908,7 @@
       <c r="CF221" s="4"/>
       <c r="CG221" s="4"/>
     </row>
-    <row r="222" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A222" s="11">
         <v>16</v>
       </c>
@@ -58198,7 +58195,7 @@
       <c r="CF222" s="4"/>
       <c r="CG222" s="4"/>
     </row>
-    <row r="223" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A223" s="11">
         <v>17</v>
       </c>
@@ -58485,7 +58482,7 @@
       <c r="CF223" s="4"/>
       <c r="CG223" s="4"/>
     </row>
-    <row r="224" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A224" s="11">
         <v>18</v>
       </c>
@@ -58772,7 +58769,7 @@
       <c r="CF224" s="4"/>
       <c r="CG224" s="4"/>
     </row>
-    <row r="225" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A225" s="11">
         <v>19</v>
       </c>
@@ -59059,7 +59056,7 @@
       <c r="CF225" s="4"/>
       <c r="CG225" s="4"/>
     </row>
-    <row r="226" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A226" s="11">
         <v>20</v>
       </c>
@@ -59346,7 +59343,7 @@
       <c r="CF226" s="4"/>
       <c r="CG226" s="4"/>
     </row>
-    <row r="227" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A227" s="11">
         <v>21</v>
       </c>
@@ -59633,7 +59630,7 @@
       <c r="CF227" s="4"/>
       <c r="CG227" s="4"/>
     </row>
-    <row r="228" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A228" s="11">
         <v>22</v>
       </c>
@@ -59920,7 +59917,7 @@
       <c r="CF228" s="4"/>
       <c r="CG228" s="4"/>
     </row>
-    <row r="229" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A229" s="11">
         <v>23</v>
       </c>
@@ -60207,7 +60204,7 @@
       <c r="CF229" s="4"/>
       <c r="CG229" s="4"/>
     </row>
-    <row r="230" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A230" s="11">
         <v>24</v>
       </c>
@@ -60494,7 +60491,7 @@
       <c r="CF230" s="4"/>
       <c r="CG230" s="4"/>
     </row>
-    <row r="231" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A231" s="11">
         <v>25</v>
       </c>
@@ -60781,7 +60778,7 @@
       <c r="CF231" s="4"/>
       <c r="CG231" s="4"/>
     </row>
-    <row r="232" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A232" s="11">
         <v>26</v>
       </c>
@@ -61068,7 +61065,7 @@
       <c r="CF232" s="4"/>
       <c r="CG232" s="4"/>
     </row>
-    <row r="233" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A233" s="11">
         <v>27</v>
       </c>
@@ -61355,7 +61352,7 @@
       <c r="CF233" s="4"/>
       <c r="CG233" s="4"/>
     </row>
-    <row r="234" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A234" s="11">
         <v>28</v>
       </c>
@@ -61642,7 +61639,7 @@
       <c r="CF234" s="4"/>
       <c r="CG234" s="4"/>
     </row>
-    <row r="235" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A235" s="11">
         <v>29</v>
       </c>
@@ -61929,7 +61926,7 @@
       <c r="CF235" s="4"/>
       <c r="CG235" s="4"/>
     </row>
-    <row r="236" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A236" s="11">
         <v>30</v>
       </c>
@@ -62216,7 +62213,7 @@
       <c r="CF236" s="4"/>
       <c r="CG236" s="4"/>
     </row>
-    <row r="237" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A237" s="11">
         <v>31</v>
       </c>
@@ -62503,7 +62500,7 @@
       <c r="CF237" s="4"/>
       <c r="CG237" s="4"/>
     </row>
-    <row r="238" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A238" s="11">
         <v>32</v>
       </c>
@@ -62790,7 +62787,7 @@
       <c r="CF238" s="4"/>
       <c r="CG238" s="4"/>
     </row>
-    <row r="239" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A239" s="11">
         <v>33</v>
       </c>
@@ -63077,7 +63074,7 @@
       <c r="CF239" s="4"/>
       <c r="CG239" s="4"/>
     </row>
-    <row r="240" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A240" s="11">
         <v>34</v>
       </c>
@@ -63364,7 +63361,7 @@
       <c r="CF240" s="4"/>
       <c r="CG240" s="4"/>
     </row>
-    <row r="241" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A241" s="11">
         <v>35</v>
       </c>
@@ -63651,7 +63648,7 @@
       <c r="CF241" s="4"/>
       <c r="CG241" s="4"/>
     </row>
-    <row r="242" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A242" s="11">
         <v>36</v>
       </c>
@@ -63938,7 +63935,7 @@
       <c r="CF242" s="4"/>
       <c r="CG242" s="4"/>
     </row>
-    <row r="243" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A243" s="11">
         <v>37</v>
       </c>
@@ -64225,7 +64222,7 @@
       <c r="CF243" s="4"/>
       <c r="CG243" s="4"/>
     </row>
-    <row r="244" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A244" s="11">
         <v>38</v>
       </c>
@@ -64512,7 +64509,7 @@
       <c r="CF244" s="4"/>
       <c r="CG244" s="4"/>
     </row>
-    <row r="245" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A245" s="11">
         <v>39</v>
       </c>
@@ -64799,7 +64796,7 @@
       <c r="CF245" s="4"/>
       <c r="CG245" s="4"/>
     </row>
-    <row r="246" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A246" s="11">
         <v>40</v>
       </c>
@@ -65086,7 +65083,7 @@
       <c r="CF246" s="4"/>
       <c r="CG246" s="4"/>
     </row>
-    <row r="247" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A247" s="11">
         <v>41</v>
       </c>
@@ -65373,7 +65370,7 @@
       <c r="CF247" s="4"/>
       <c r="CG247" s="4"/>
     </row>
-    <row r="248" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A248" s="11">
         <v>42</v>
       </c>
@@ -65660,7 +65657,7 @@
       <c r="CF248" s="4"/>
       <c r="CG248" s="4"/>
     </row>
-    <row r="249" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A249" s="11">
         <v>43</v>
       </c>
@@ -65947,7 +65944,7 @@
       <c r="CF249" s="4"/>
       <c r="CG249" s="4"/>
     </row>
-    <row r="250" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A250" s="11">
         <v>44</v>
       </c>
@@ -66234,7 +66231,7 @@
       <c r="CF250" s="4"/>
       <c r="CG250" s="4"/>
     </row>
-    <row r="251" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A251" s="11">
         <v>45</v>
       </c>
@@ -66521,7 +66518,7 @@
       <c r="CF251" s="4"/>
       <c r="CG251" s="4"/>
     </row>
-    <row r="252" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A252" s="11">
         <v>46</v>
       </c>
@@ -66808,7 +66805,7 @@
       <c r="CF252" s="4"/>
       <c r="CG252" s="4"/>
     </row>
-    <row r="253" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A253" s="11">
         <v>47</v>
       </c>
@@ -67095,7 +67092,7 @@
       <c r="CF253" s="4"/>
       <c r="CG253" s="4"/>
     </row>
-    <row r="254" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A254" s="11">
         <v>48</v>
       </c>
@@ -67382,7 +67379,7 @@
       <c r="CF254" s="4"/>
       <c r="CG254" s="4"/>
     </row>
-    <row r="255" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A255" s="11">
         <v>49</v>
       </c>
@@ -67669,7 +67666,7 @@
       <c r="CF255" s="4"/>
       <c r="CG255" s="4"/>
     </row>
-    <row r="256" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A256" s="11">
         <v>50</v>
       </c>
@@ -67956,7 +67953,7 @@
       <c r="CF256" s="4"/>
       <c r="CG256" s="4"/>
     </row>
-    <row r="257" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A257" s="11">
         <v>51</v>
       </c>
@@ -68243,7 +68240,7 @@
       <c r="CF257" s="4"/>
       <c r="CG257" s="4"/>
     </row>
-    <row r="258" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A258" s="11">
         <v>52</v>
       </c>
@@ -68530,7 +68527,7 @@
       <c r="CF258" s="4"/>
       <c r="CG258" s="4"/>
     </row>
-    <row r="259" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A259" s="11">
         <v>53</v>
       </c>
@@ -68817,7 +68814,7 @@
       <c r="CF259" s="4"/>
       <c r="CG259" s="4"/>
     </row>
-    <row r="260" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A260" s="11">
         <v>54</v>
       </c>
@@ -69104,7 +69101,7 @@
       <c r="CF260" s="4"/>
       <c r="CG260" s="4"/>
     </row>
-    <row r="261" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A261" s="11">
         <v>55</v>
       </c>
@@ -69391,7 +69388,7 @@
       <c r="CF261" s="4"/>
       <c r="CG261" s="4"/>
     </row>
-    <row r="262" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A262" s="11">
         <v>56</v>
       </c>
@@ -69678,7 +69675,7 @@
       <c r="CF262" s="4"/>
       <c r="CG262" s="4"/>
     </row>
-    <row r="263" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A263" s="11">
         <v>57</v>
       </c>
@@ -69965,7 +69962,7 @@
       <c r="CF263" s="4"/>
       <c r="CG263" s="4"/>
     </row>
-    <row r="264" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A264" s="11">
         <v>58</v>
       </c>
@@ -70252,7 +70249,7 @@
       <c r="CF264" s="4"/>
       <c r="CG264" s="4"/>
     </row>
-    <row r="265" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A265" s="11">
         <v>59</v>
       </c>
@@ -70539,7 +70536,7 @@
       <c r="CF265" s="4"/>
       <c r="CG265" s="4"/>
     </row>
-    <row r="266" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A266" s="11">
         <v>60</v>
       </c>
@@ -70826,7 +70823,7 @@
       <c r="CF266" s="4"/>
       <c r="CG266" s="4"/>
     </row>
-    <row r="267" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A267" s="11">
         <v>61</v>
       </c>
@@ -71113,7 +71110,7 @@
       <c r="CF267" s="4"/>
       <c r="CG267" s="4"/>
     </row>
-    <row r="268" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A268" s="11">
         <v>62</v>
       </c>
@@ -71400,7 +71397,7 @@
       <c r="CF268" s="4"/>
       <c r="CG268" s="4"/>
     </row>
-    <row r="269" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A269" s="11">
         <v>63</v>
       </c>
@@ -71687,7 +71684,7 @@
       <c r="CF269" s="4"/>
       <c r="CG269" s="4"/>
     </row>
-    <row r="270" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A270" s="11">
         <v>64</v>
       </c>
@@ -71974,7 +71971,7 @@
       <c r="CF270" s="4"/>
       <c r="CG270" s="4"/>
     </row>
-    <row r="271" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A271" s="11">
         <v>65</v>
       </c>
@@ -72261,7 +72258,7 @@
       <c r="CF271" s="4"/>
       <c r="CG271" s="4"/>
     </row>
-    <row r="272" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A272" s="11">
         <v>66</v>
       </c>
@@ -72548,7 +72545,7 @@
       <c r="CF272" s="4"/>
       <c r="CG272" s="4"/>
     </row>
-    <row r="273" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A273" s="11">
         <v>67</v>
       </c>
@@ -72835,7 +72832,7 @@
       <c r="CF273" s="4"/>
       <c r="CG273" s="4"/>
     </row>
-    <row r="274" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A274" s="11">
         <v>68</v>
       </c>
@@ -73122,7 +73119,7 @@
       <c r="CF274" s="4"/>
       <c r="CG274" s="4"/>
     </row>
-    <row r="275" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A275" s="11">
         <v>69</v>
       </c>
@@ -73409,7 +73406,7 @@
       <c r="CF275" s="4"/>
       <c r="CG275" s="4"/>
     </row>
-    <row r="276" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A276" s="11">
         <v>70</v>
       </c>
@@ -73696,7 +73693,7 @@
       <c r="CF276" s="4"/>
       <c r="CG276" s="4"/>
     </row>
-    <row r="277" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A277" s="11">
         <v>71</v>
       </c>
@@ -73983,7 +73980,7 @@
       <c r="CF277" s="4"/>
       <c r="CG277" s="4"/>
     </row>
-    <row r="278" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A278" s="11">
         <v>72</v>
       </c>
@@ -74270,7 +74267,7 @@
       <c r="CF278" s="4"/>
       <c r="CG278" s="4"/>
     </row>
-    <row r="279" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A279" s="11">
         <v>73</v>
       </c>
@@ -74557,7 +74554,7 @@
       <c r="CF279" s="4"/>
       <c r="CG279" s="4"/>
     </row>
-    <row r="280" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A280" s="11">
         <v>74</v>
       </c>
@@ -74844,7 +74841,7 @@
       <c r="CF280" s="4"/>
       <c r="CG280" s="4"/>
     </row>
-    <row r="281" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A281" s="11">
         <v>75</v>
       </c>
@@ -75131,7 +75128,7 @@
       <c r="CF281" s="4"/>
       <c r="CG281" s="4"/>
     </row>
-    <row r="282" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A282" s="11">
         <v>76</v>
       </c>
@@ -75418,7 +75415,7 @@
       <c r="CF282" s="4"/>
       <c r="CG282" s="4"/>
     </row>
-    <row r="283" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A283" s="11">
         <v>77</v>
       </c>
@@ -75705,7 +75702,7 @@
       <c r="CF283" s="4"/>
       <c r="CG283" s="4"/>
     </row>
-    <row r="284" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A284" s="11">
         <v>78</v>
       </c>
@@ -75992,7 +75989,7 @@
       <c r="CF284" s="4"/>
       <c r="CG284" s="4"/>
     </row>
-    <row r="285" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A285" s="11">
         <v>79</v>
       </c>
@@ -76279,7 +76276,7 @@
       <c r="CF285" s="4"/>
       <c r="CG285" s="4"/>
     </row>
-    <row r="286" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A286" s="11">
         <v>80</v>
       </c>
@@ -76566,7 +76563,7 @@
       <c r="CF286" s="4"/>
       <c r="CG286" s="4"/>
     </row>
-    <row r="287" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A287" s="11">
         <v>81</v>
       </c>
@@ -76853,7 +76850,7 @@
       <c r="CF287" s="4"/>
       <c r="CG287" s="4"/>
     </row>
-    <row r="288" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A288" s="11">
         <v>82</v>
       </c>
@@ -77140,7 +77137,7 @@
       <c r="CF288" s="4"/>
       <c r="CG288" s="4"/>
     </row>
-    <row r="289" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A289" s="11">
         <v>83</v>
       </c>
@@ -77427,7 +77424,7 @@
       <c r="CF289" s="4"/>
       <c r="CG289" s="4"/>
     </row>
-    <row r="290" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A290" s="11">
         <v>84</v>
       </c>
@@ -77714,7 +77711,7 @@
       <c r="CF290" s="4"/>
       <c r="CG290" s="4"/>
     </row>
-    <row r="291" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A291" s="11">
         <v>85</v>
       </c>
@@ -78001,7 +77998,7 @@
       <c r="CF291" s="4"/>
       <c r="CG291" s="4"/>
     </row>
-    <row r="292" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A292" s="11">
         <v>86</v>
       </c>
@@ -78288,7 +78285,7 @@
       <c r="CF292" s="4"/>
       <c r="CG292" s="4"/>
     </row>
-    <row r="293" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A293" s="11">
         <v>87</v>
       </c>
@@ -78575,7 +78572,7 @@
       <c r="CF293" s="4"/>
       <c r="CG293" s="4"/>
     </row>
-    <row r="294" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A294" s="11">
         <v>88</v>
       </c>
@@ -78862,7 +78859,7 @@
       <c r="CF294" s="4"/>
       <c r="CG294" s="4"/>
     </row>
-    <row r="295" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A295" s="11">
         <v>89</v>
       </c>
@@ -79149,7 +79146,7 @@
       <c r="CF295" s="4"/>
       <c r="CG295" s="4"/>
     </row>
-    <row r="296" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A296" s="11">
         <v>90</v>
       </c>
@@ -79436,7 +79433,7 @@
       <c r="CF296" s="4"/>
       <c r="CG296" s="4"/>
     </row>
-    <row r="297" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A297" s="11">
         <v>91</v>
       </c>
@@ -79723,7 +79720,7 @@
       <c r="CF297" s="4"/>
       <c r="CG297" s="4"/>
     </row>
-    <row r="298" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A298" s="11">
         <v>92</v>
       </c>
@@ -80010,7 +80007,7 @@
       <c r="CF298" s="4"/>
       <c r="CG298" s="4"/>
     </row>
-    <row r="299" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A299" s="11">
         <v>93</v>
       </c>
@@ -80297,7 +80294,7 @@
       <c r="CF299" s="4"/>
       <c r="CG299" s="4"/>
     </row>
-    <row r="300" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A300" s="11">
         <v>94</v>
       </c>
@@ -80584,7 +80581,7 @@
       <c r="CF300" s="4"/>
       <c r="CG300" s="4"/>
     </row>
-    <row r="301" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A301" s="11">
         <v>95</v>
       </c>
@@ -80871,7 +80868,7 @@
       <c r="CF301" s="4"/>
       <c r="CG301" s="4"/>
     </row>
-    <row r="302" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A302" s="11">
         <v>96</v>
       </c>
@@ -81158,7 +81155,7 @@
       <c r="CF302" s="4"/>
       <c r="CG302" s="4"/>
     </row>
-    <row r="303" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A303" s="11">
         <v>97</v>
       </c>
@@ -81445,7 +81442,7 @@
       <c r="CF303" s="4"/>
       <c r="CG303" s="4"/>
     </row>
-    <row r="304" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A304" s="11">
         <v>98</v>
       </c>
@@ -81732,7 +81729,7 @@
       <c r="CF304" s="4"/>
       <c r="CG304" s="4"/>
     </row>
-    <row r="305" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A305" s="11">
         <v>99</v>
       </c>
@@ -82019,7 +82016,7 @@
       <c r="CF305" s="4"/>
       <c r="CG305" s="4"/>
     </row>
-    <row r="306" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A306" s="11">
         <v>100</v>
       </c>
@@ -82306,7 +82303,7 @@
       <c r="CF306" s="4"/>
       <c r="CG306" s="4"/>
     </row>
-    <row r="307" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A307" s="11">
         <v>101</v>
       </c>
@@ -82593,7 +82590,7 @@
       <c r="CF307" s="4"/>
       <c r="CG307" s="4"/>
     </row>
-    <row r="308" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A308" s="11">
         <v>102</v>
       </c>
@@ -82880,7 +82877,7 @@
       <c r="CF308" s="4"/>
       <c r="CG308" s="4"/>
     </row>
-    <row r="309" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A309" s="11">
         <v>103</v>
       </c>
@@ -83167,7 +83164,7 @@
       <c r="CF309" s="4"/>
       <c r="CG309" s="4"/>
     </row>
-    <row r="310" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A310" s="11">
         <v>104</v>
       </c>
@@ -83454,7 +83451,7 @@
       <c r="CF310" s="4"/>
       <c r="CG310" s="4"/>
     </row>
-    <row r="311" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A311" s="11">
         <v>105</v>
       </c>
@@ -83741,7 +83738,7 @@
       <c r="CF311" s="4"/>
       <c r="CG311" s="4"/>
     </row>
-    <row r="312" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A312" s="11">
         <v>106</v>
       </c>
@@ -84028,7 +84025,7 @@
       <c r="CF312" s="4"/>
       <c r="CG312" s="4"/>
     </row>
-    <row r="313" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A313" s="11">
         <v>107</v>
       </c>
@@ -84315,7 +84312,7 @@
       <c r="CF313" s="4"/>
       <c r="CG313" s="4"/>
     </row>
-    <row r="314" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A314" s="11">
         <v>108</v>
       </c>
@@ -84602,7 +84599,7 @@
       <c r="CF314" s="4"/>
       <c r="CG314" s="4"/>
     </row>
-    <row r="315" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A315" s="11">
         <v>109</v>
       </c>
@@ -84889,7 +84886,7 @@
       <c r="CF315" s="4"/>
       <c r="CG315" s="4"/>
     </row>
-    <row r="316" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A316" s="11">
         <v>110</v>
       </c>
@@ -85176,7 +85173,7 @@
       <c r="CF316" s="4"/>
       <c r="CG316" s="4"/>
     </row>
-    <row r="317" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A317" s="11">
         <v>111</v>
       </c>
@@ -85463,7 +85460,7 @@
       <c r="CF317" s="4"/>
       <c r="CG317" s="4"/>
     </row>
-    <row r="318" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A318" s="11">
         <v>112</v>
       </c>
@@ -85750,7 +85747,7 @@
       <c r="CF318" s="4"/>
       <c r="CG318" s="4"/>
     </row>
-    <row r="319" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A319" s="11">
         <v>113</v>
       </c>
